--- a/fx-server/资源/题库/题目A.xlsx
+++ b/fx-server/资源/题库/题目A.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28155" windowHeight="13185"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="0" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="454">
   <si>
     <t>阶段编号</t>
   </si>
@@ -81,45 +81,68 @@
     <t>单选题</t>
   </si>
   <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.png</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1个月</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2个月</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3个月</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6个月</t>
+  </si>
+  <si>
+    <r>
+      <t>图片5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>文字</t>
-  </si>
-  <si>
-    <t xml:space="preserve">退役军人职业技能培训最短不少于（   ）。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1个月</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2个月</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3个月</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6个月</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">县级以上地方人民政府每年至少组织（   ）次退役军人专场招聘活动，为其就业搭建平台。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t xml:space="preserve">申请享受光荣院集中供养、优惠服务，应当由本人向（   ）村（社区）退役军人服务站提出申请。
@@ -233,6 +256,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 当地居民的人均可支配收入水平</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t xml:space="preserve">享受定期抚恤金的烈士遗属户口迁移的，户口迁入地的县级人民政府退役军人事务部门凭定期抚恤金转移证明，从（   ）起发放定期抚恤金。
@@ -3973,7 +3999,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -4004,6 +4030,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -4013,12 +4045,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4193,11 +4219,6 @@
     <font>
       <sz val="10.5"/>
       <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4684,20 +4705,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -5098,8 +5119,8 @@
       <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -5115,7 +5136,7 @@
         <v>22</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="2"/>
@@ -5134,24 +5155,24 @@
         <v>17</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" s="2"/>
     </row>
@@ -5166,7 +5187,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
@@ -5178,10 +5199,10 @@
       <c r="H4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="6" t="s">
         <v>34</v>
       </c>
       <c r="K4" s="4"/>
@@ -5201,7 +5222,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="4" t="s">
@@ -5236,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="4" t="s">
@@ -5271,7 +5292,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="4" t="s">
@@ -5291,7 +5312,7 @@
       </c>
       <c r="K7" s="4"/>
       <c r="M7" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O7" s="2"/>
     </row>
@@ -5306,23 +5327,23 @@
         <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" s="4"/>
       <c r="M8" s="4" t="s">
@@ -5341,27 +5362,27 @@
         <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O9" s="2"/>
     </row>
@@ -5376,27 +5397,27 @@
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="K10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -5411,27 +5432,27 @@
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="K11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O11" s="2"/>
     </row>
@@ -5446,27 +5467,27 @@
         <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O12" s="2"/>
     </row>
@@ -5481,23 +5502,23 @@
         <v>16</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K13" s="4"/>
       <c r="M13" s="4" t="s">
@@ -5516,23 +5537,23 @@
         <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K14" s="4"/>
       <c r="M14" s="4" t="s">
@@ -5551,23 +5572,23 @@
         <v>16</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K15" s="4"/>
       <c r="M15" s="4" t="s">
@@ -5586,14 +5607,14 @@
         <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>37</v>
@@ -5606,7 +5627,7 @@
       </c>
       <c r="K16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O16" s="2"/>
     </row>
@@ -5621,27 +5642,27 @@
         <v>16</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O17" s="2"/>
     </row>
@@ -5656,11 +5677,11 @@
         <v>16</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>19</v>
@@ -5672,11 +5693,11 @@
         <v>22</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O18" s="2"/>
     </row>
@@ -5691,27 +5712,27 @@
         <v>16</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O19" s="2"/>
     </row>
@@ -5726,27 +5747,27 @@
         <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O20" s="2"/>
     </row>
@@ -5761,27 +5782,27 @@
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O21" s="2"/>
     </row>
@@ -5793,30 +5814,30 @@
         <v>15</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -5828,30 +5849,30 @@
         <v>15</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O23" s="2"/>
     </row>
@@ -5863,30 +5884,30 @@
         <v>15</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -5898,30 +5919,30 @@
         <v>15</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -5933,30 +5954,30 @@
         <v>15</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -5968,30 +5989,30 @@
         <v>15</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -6003,30 +6024,30 @@
         <v>15</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -6038,30 +6059,30 @@
         <v>15</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -6073,30 +6094,30 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -6108,30 +6129,30 @@
         <v>15</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O31" s="2"/>
     </row>
@@ -6143,30 +6164,30 @@
         <v>15</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -6178,30 +6199,30 @@
         <v>15</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -6213,30 +6234,30 @@
         <v>15</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -6248,30 +6269,30 @@
         <v>15</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -6283,30 +6304,30 @@
         <v>15</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O36" s="2"/>
     </row>
@@ -6318,30 +6339,30 @@
         <v>15</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -6353,30 +6374,30 @@
         <v>15</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -6388,30 +6409,30 @@
         <v>15</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -6423,30 +6444,30 @@
         <v>15</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -6458,30 +6479,30 @@
         <v>15</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="2"/>
     </row>
@@ -6492,24 +6513,24 @@
       <c r="B42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>213</v>
+      <c r="C42" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5" t="s">
+      <c r="F42" s="8" t="s">
         <v>215</v>
+      </c>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6521,24 +6542,24 @@
       <c r="B43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>213</v>
+      <c r="C43" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5" t="s">
+      <c r="F43" s="8" t="s">
         <v>217</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6550,15 +6571,15 @@
       <c r="B44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>213</v>
+      <c r="C44" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="6" t="s">
-        <v>218</v>
+      <c r="F44" s="8" t="s">
+        <v>219</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -6566,8 +6587,8 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-      <c r="M44" s="5" t="s">
-        <v>217</v>
+      <c r="M44" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6579,15 +6600,15 @@
       <c r="B45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>213</v>
+      <c r="C45" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="6" t="s">
-        <v>219</v>
+      <c r="F45" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -6595,8 +6616,8 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
-      <c r="M45" s="5" t="s">
-        <v>217</v>
+      <c r="M45" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6608,15 +6629,15 @@
       <c r="B46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>213</v>
+      <c r="C46" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="6" t="s">
-        <v>220</v>
+      <c r="F46" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -6624,8 +6645,8 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
-      <c r="M46" s="5" t="s">
-        <v>217</v>
+      <c r="M46" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6638,14 +6659,14 @@
         <v>15</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E47" s="2"/>
-      <c r="F47" s="6" t="s">
-        <v>222</v>
+      <c r="F47" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -6667,14 +6688,14 @@
         <v>15</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E48" s="2"/>
-      <c r="F48" s="6" t="s">
-        <v>223</v>
+      <c r="F48" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -6683,7 +6704,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6696,14 +6717,14 @@
         <v>15</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="6" t="s">
-        <v>225</v>
+      <c r="F49" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -6711,8 +6732,8 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
-      <c r="M49" s="12" t="s">
-        <v>226</v>
+      <c r="M49" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6725,14 +6746,14 @@
         <v>15</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="6" t="s">
-        <v>227</v>
+      <c r="F50" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -6754,14 +6775,14 @@
         <v>15</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E51" s="2"/>
-      <c r="F51" s="6" t="s">
-        <v>228</v>
+      <c r="F51" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -6770,7 +6791,7 @@
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6779,34 +6800,34 @@
       <c r="A52" s="2">
         <v>2</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C52" s="8" t="s">
+      <c r="B52" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="G52" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="12"/>
+      <c r="F52" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="G52" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="H52" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="I52" s="11" t="s">
         <v>235</v>
       </c>
+      <c r="J52" s="11" t="s">
+        <v>236</v>
+      </c>
       <c r="K52" s="13"/>
-      <c r="L52" s="8"/>
-      <c r="M52" s="8" t="s">
+      <c r="L52" s="11"/>
+      <c r="M52" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N52" s="2"/>
@@ -6816,34 +6837,34 @@
       <c r="A53" s="2">
         <v>2</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C53" s="8" t="s">
+      <c r="B53" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C53" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="G53" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="12"/>
+      <c r="F53" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="G53" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="H53" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J53" s="8" t="s">
+      <c r="I53" s="11" t="s">
         <v>240</v>
       </c>
+      <c r="J53" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="K53" s="13"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8" t="s">
+      <c r="L53" s="11"/>
+      <c r="M53" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N53" s="2"/>
@@ -6853,35 +6874,35 @@
       <c r="A54" s="2">
         <v>2</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C54" s="8" t="s">
+      <c r="B54" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H54" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="12"/>
+      <c r="F54" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="G54" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="H54" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="I54" s="11" t="s">
         <v>88</v>
       </c>
+      <c r="J54" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="K54" s="13"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8" t="s">
-        <v>29</v>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6890,34 +6911,34 @@
       <c r="A55" s="2">
         <v>2</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C55" s="8" t="s">
+      <c r="B55" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="G55" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="12"/>
+      <c r="F55" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="G55" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="H55" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="J55" s="8" t="s">
+      <c r="I55" s="11" t="s">
         <v>246</v>
       </c>
+      <c r="J55" s="11" t="s">
+        <v>247</v>
+      </c>
       <c r="K55" s="13"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8" t="s">
+      <c r="L55" s="11"/>
+      <c r="M55" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N55" s="2"/>
@@ -6927,34 +6948,34 @@
       <c r="A56" s="2">
         <v>2</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C56" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G56" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="12"/>
+      <c r="F56" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="G56" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="H56" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="I56" s="11" t="s">
         <v>251</v>
       </c>
+      <c r="J56" s="11" t="s">
+        <v>252</v>
+      </c>
       <c r="K56" s="13"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8" t="s">
+      <c r="L56" s="11"/>
+      <c r="M56" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N56" s="2"/>
@@ -6964,35 +6985,35 @@
       <c r="A57" s="2">
         <v>2</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C57" s="8" t="s">
+      <c r="B57" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C57" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="G57" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="12"/>
+      <c r="F57" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="J57" s="8" t="s">
+      <c r="I57" s="11" t="s">
         <v>254</v>
       </c>
+      <c r="J57" s="11" t="s">
+        <v>255</v>
+      </c>
       <c r="K57" s="13"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8" t="s">
-        <v>23</v>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7001,35 +7022,35 @@
       <c r="A58" s="2">
         <v>2</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="G58" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="G58" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="H58" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="I58" s="11" t="s">
         <v>259</v>
       </c>
+      <c r="J58" s="11" t="s">
+        <v>260</v>
+      </c>
       <c r="K58" s="13"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8" t="s">
-        <v>23</v>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7038,34 +7059,34 @@
       <c r="A59" s="2">
         <v>2</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C59" s="8" t="s">
+      <c r="B59" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C59" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G59" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="12"/>
+      <c r="F59" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="G59" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="H59" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="J59" s="8" t="s">
+      <c r="I59" s="11" t="s">
         <v>264</v>
       </c>
+      <c r="J59" s="11" t="s">
+        <v>265</v>
+      </c>
       <c r="K59" s="13"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8" t="s">
+      <c r="L59" s="11"/>
+      <c r="M59" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N59" s="2"/>
@@ -7075,34 +7096,34 @@
       <c r="A60" s="2">
         <v>2</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C60" s="8" t="s">
+      <c r="B60" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="G60" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="12"/>
+      <c r="F60" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="G60" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="I60" s="8" t="s">
+      <c r="H60" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="J60" s="8" t="s">
+      <c r="I60" s="11" t="s">
         <v>269</v>
       </c>
+      <c r="J60" s="11" t="s">
+        <v>270</v>
+      </c>
       <c r="K60" s="13"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="8" t="s">
+      <c r="L60" s="11"/>
+      <c r="M60" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N60" s="2"/>
@@ -7112,35 +7133,35 @@
       <c r="A61" s="2">
         <v>2</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C61" s="8" t="s">
+      <c r="B61" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G61" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="12"/>
+      <c r="F61" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="G61" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="I61" s="8" t="s">
+      <c r="H61" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="J61" s="8" t="s">
+      <c r="I61" s="11" t="s">
         <v>274</v>
       </c>
+      <c r="J61" s="11" t="s">
+        <v>275</v>
+      </c>
       <c r="K61" s="13"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8" t="s">
-        <v>29</v>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7149,34 +7170,34 @@
       <c r="A62" s="2">
         <v>2</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C62" s="8" t="s">
+      <c r="B62" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C62" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="G62" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="12"/>
+      <c r="F62" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="H62" s="8" t="s">
+      <c r="G62" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="I62" s="8" t="s">
+      <c r="H62" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="J62" s="8" t="s">
+      <c r="I62" s="11" t="s">
         <v>279</v>
       </c>
+      <c r="J62" s="11" t="s">
+        <v>280</v>
+      </c>
       <c r="K62" s="13"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="8" t="s">
+      <c r="L62" s="11"/>
+      <c r="M62" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N62" s="2"/>
@@ -7186,34 +7207,34 @@
       <c r="A63" s="2">
         <v>2</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C63" s="8" t="s">
+      <c r="B63" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C63" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="G63" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="12"/>
+      <c r="F63" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="G63" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="I63" s="8" t="s">
+      <c r="H63" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="J63" s="8" t="s">
+      <c r="I63" s="11" t="s">
         <v>284</v>
       </c>
+      <c r="J63" s="11" t="s">
+        <v>285</v>
+      </c>
       <c r="K63" s="13"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8" t="s">
+      <c r="L63" s="11"/>
+      <c r="M63" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N63" s="2"/>
@@ -7223,35 +7244,35 @@
       <c r="A64" s="2">
         <v>2</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C64" s="8" t="s">
+      <c r="B64" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="G64" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="G64" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="I64" s="8" t="s">
+      <c r="H64" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="J64" s="8" t="s">
+      <c r="I64" s="11" t="s">
         <v>289</v>
       </c>
+      <c r="J64" s="11" t="s">
+        <v>290</v>
+      </c>
       <c r="K64" s="13"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8" t="s">
-        <v>23</v>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7260,35 +7281,35 @@
       <c r="A65" s="2">
         <v>2</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C65" s="8" t="s">
+      <c r="B65" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="G65" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="12"/>
+      <c r="F65" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="G65" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="I65" s="8" t="s">
+      <c r="H65" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="J65" s="8" t="s">
+      <c r="I65" s="11" t="s">
         <v>294</v>
       </c>
+      <c r="J65" s="11" t="s">
+        <v>295</v>
+      </c>
       <c r="K65" s="13"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="8" t="s">
-        <v>23</v>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7297,34 +7318,34 @@
       <c r="A66" s="2">
         <v>2</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C66" s="8" t="s">
+      <c r="B66" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H66" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="I66" s="8" t="s">
+      <c r="G66" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="J66" s="8" t="s">
+      <c r="I66" s="11" t="s">
         <v>298</v>
       </c>
+      <c r="J66" s="11" t="s">
+        <v>299</v>
+      </c>
       <c r="K66" s="13"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="8" t="s">
+      <c r="L66" s="11"/>
+      <c r="M66" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N66" s="2"/>
@@ -7334,35 +7355,35 @@
       <c r="A67" s="2">
         <v>2</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C67" s="8" t="s">
+      <c r="B67" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="G67" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="12"/>
+      <c r="F67" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="H67" s="8" t="s">
+      <c r="G67" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="I67" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="J67" s="8" t="s">
+      <c r="H67" s="11" t="s">
         <v>302</v>
       </c>
+      <c r="I67" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>303</v>
+      </c>
       <c r="K67" s="13"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8" t="s">
-        <v>23</v>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -7371,35 +7392,35 @@
       <c r="A68" s="2">
         <v>2</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C68" s="8" t="s">
+      <c r="B68" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C68" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="G68" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="12"/>
+      <c r="F68" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="G68" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="H68" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="J68" s="8" t="s">
+      <c r="I68" s="11" t="s">
         <v>307</v>
       </c>
+      <c r="J68" s="11" t="s">
+        <v>308</v>
+      </c>
       <c r="K68" s="13"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8" t="s">
-        <v>29</v>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -7408,34 +7429,34 @@
       <c r="A69" s="2">
         <v>2</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C69" s="8" t="s">
+      <c r="B69" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="G69" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="12"/>
+      <c r="F69" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="G69" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="H69" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="J69" s="8" t="s">
+      <c r="I69" s="11" t="s">
         <v>312</v>
       </c>
+      <c r="J69" s="11" t="s">
+        <v>313</v>
+      </c>
       <c r="K69" s="13"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8" t="s">
+      <c r="L69" s="11"/>
+      <c r="M69" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N69" s="2"/>
@@ -7445,35 +7466,35 @@
       <c r="A70" s="2">
         <v>2</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C70" s="8" t="s">
+      <c r="B70" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="G70" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="12"/>
+      <c r="F70" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="G70" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="I70" s="8" t="s">
+      <c r="H70" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="J70" s="8" t="s">
+      <c r="I70" s="11" t="s">
         <v>317</v>
       </c>
+      <c r="J70" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="K70" s="13"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8" t="s">
-        <v>29</v>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -7482,34 +7503,34 @@
       <c r="A71" s="2">
         <v>2</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C71" s="8" t="s">
+      <c r="B71" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C71" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="G71" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="12"/>
+      <c r="F71" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="H71" s="8" t="s">
+      <c r="G71" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="I71" s="8" t="s">
+      <c r="H71" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="I71" s="11" t="s">
         <v>322</v>
       </c>
+      <c r="J71" s="11" t="s">
+        <v>323</v>
+      </c>
       <c r="K71" s="13"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8" t="s">
+      <c r="L71" s="11"/>
+      <c r="M71" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N71" s="2"/>
@@ -7519,35 +7540,35 @@
       <c r="A72" s="2">
         <v>3</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>105</v>
+      <c r="B72" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="G72" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="12"/>
+      <c r="F72" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="G72" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="I72" s="8" t="s">
+      <c r="H72" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="J72" s="8" t="s">
+      <c r="I72" s="11" t="s">
         <v>328</v>
       </c>
+      <c r="J72" s="11" t="s">
+        <v>329</v>
+      </c>
       <c r="K72" s="13"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8" t="s">
-        <v>144</v>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -7556,34 +7577,34 @@
       <c r="A73" s="2">
         <v>3</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C73" s="8" t="s">
+      <c r="B73" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C73" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="G73" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="12"/>
+      <c r="F73" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="G73" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="I73" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="J73" s="8" t="s">
+      <c r="H73" s="11" t="s">
         <v>332</v>
       </c>
+      <c r="I73" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>333</v>
+      </c>
       <c r="K73" s="13"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8" t="s">
+      <c r="L73" s="11"/>
+      <c r="M73" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N73" s="2"/>
@@ -7593,34 +7614,34 @@
       <c r="A74" s="2">
         <v>3</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C74" s="8" t="s">
+      <c r="B74" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G74" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="12"/>
+      <c r="F74" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="G74" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="I74" s="8" t="s">
+      <c r="H74" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="J74" s="8" t="s">
+      <c r="I74" s="11" t="s">
         <v>337</v>
       </c>
+      <c r="J74" s="11" t="s">
+        <v>338</v>
+      </c>
       <c r="K74" s="13"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8" t="s">
+      <c r="L74" s="11"/>
+      <c r="M74" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N74" s="2"/>
@@ -7630,34 +7651,34 @@
       <c r="A75" s="2">
         <v>3</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="8" t="s">
+      <c r="B75" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C75" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E75" s="12"/>
       <c r="F75" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="G75" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="H75" s="8" t="s">
+      <c r="G75" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="I75" s="8" t="s">
+      <c r="H75" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="J75" s="8" t="s">
-        <v>341</v>
+      <c r="I75" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>342</v>
       </c>
       <c r="K75" s="13"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8" t="s">
+      <c r="L75" s="11"/>
+      <c r="M75" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N75" s="2"/>
@@ -7667,35 +7688,35 @@
       <c r="A76" s="2">
         <v>3</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C76" s="8" t="s">
+      <c r="B76" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C76" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="G76" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="12"/>
+      <c r="F76" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="H76" s="8" t="s">
+      <c r="G76" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="I76" s="8" t="s">
+      <c r="H76" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="J76" s="8" t="s">
+      <c r="I76" s="11" t="s">
         <v>346</v>
       </c>
+      <c r="J76" s="11" t="s">
+        <v>347</v>
+      </c>
       <c r="K76" s="13"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8" t="s">
-        <v>29</v>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -7704,35 +7725,35 @@
       <c r="A77" s="2">
         <v>3</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>105</v>
+      <c r="B77" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="G77" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="12"/>
+      <c r="F77" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="G77" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="I77" s="8" t="s">
+      <c r="H77" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="J77" s="8" t="s">
+      <c r="I77" s="11" t="s">
         <v>351</v>
       </c>
+      <c r="J77" s="11" t="s">
+        <v>352</v>
+      </c>
       <c r="K77" s="13"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8" t="s">
-        <v>128</v>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -7741,35 +7762,35 @@
       <c r="A78" s="2">
         <v>3</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C78" s="8" t="s">
+      <c r="B78" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C78" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H78" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="12"/>
+      <c r="F78" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G78" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="I78" s="8" t="s">
+      <c r="H78" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="J78" s="8" t="s">
-        <v>76</v>
+      <c r="I78" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="K78" s="13"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8" t="s">
-        <v>29</v>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -7778,34 +7799,34 @@
       <c r="A79" s="2">
         <v>3</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C79" s="8" t="s">
+      <c r="B79" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="G79" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="12"/>
+      <c r="F79" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="H79" s="8" t="s">
+      <c r="G79" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="I79" s="8" t="s">
+      <c r="H79" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="J79" s="8" t="s">
+      <c r="I79" s="11" t="s">
         <v>357</v>
       </c>
+      <c r="J79" s="11" t="s">
+        <v>358</v>
+      </c>
       <c r="K79" s="13"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8" t="s">
+      <c r="L79" s="11"/>
+      <c r="M79" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N79" s="2"/>
@@ -7815,34 +7836,34 @@
       <c r="A80" s="2">
         <v>3</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C80" s="8" t="s">
+      <c r="B80" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C80" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="G80" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="12"/>
+      <c r="F80" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="G80" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="I80" s="8" t="s">
+      <c r="H80" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="J80" s="8" t="s">
+      <c r="I80" s="11" t="s">
         <v>362</v>
       </c>
+      <c r="J80" s="11" t="s">
+        <v>363</v>
+      </c>
       <c r="K80" s="13"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8" t="s">
+      <c r="L80" s="11"/>
+      <c r="M80" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N80" s="2"/>
@@ -7852,35 +7873,35 @@
       <c r="A81" s="2">
         <v>3</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C81" s="8" t="s">
+      <c r="B81" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C81" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="G81" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="12"/>
+      <c r="F81" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="H81" s="8" t="s">
+      <c r="G81" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="I81" s="8" t="s">
+      <c r="H81" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="J81" s="8" t="s">
+      <c r="I81" s="11" t="s">
         <v>367</v>
       </c>
+      <c r="J81" s="11" t="s">
+        <v>368</v>
+      </c>
       <c r="K81" s="13"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8" t="s">
-        <v>23</v>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -7889,35 +7910,35 @@
       <c r="A82" s="2">
         <v>3</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C82" s="8" t="s">
+      <c r="B82" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C82" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="G82" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="12"/>
+      <c r="F82" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="H82" s="8" t="s">
+      <c r="G82" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="I82" s="8" t="s">
+      <c r="H82" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="J82" s="8" t="s">
+      <c r="I82" s="11" t="s">
         <v>372</v>
       </c>
+      <c r="J82" s="11" t="s">
+        <v>373</v>
+      </c>
       <c r="K82" s="13"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8" t="s">
-        <v>23</v>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -7926,35 +7947,35 @@
       <c r="A83" s="2">
         <v>3</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C83" s="8" t="s">
+      <c r="B83" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C83" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="G83" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="12"/>
+      <c r="F83" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="H83" s="8" t="s">
+      <c r="G83" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="I83" s="8" t="s">
+      <c r="H83" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="J83" s="8" t="s">
+      <c r="I83" s="11" t="s">
         <v>377</v>
       </c>
+      <c r="J83" s="11" t="s">
+        <v>378</v>
+      </c>
       <c r="K83" s="13"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8" t="s">
-        <v>29</v>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -7963,35 +7984,35 @@
       <c r="A84" s="2">
         <v>3</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C84" s="8" t="s">
+      <c r="B84" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C84" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="G84" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="12"/>
+      <c r="F84" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="H84" s="8" t="s">
+      <c r="G84" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="I84" s="8" t="s">
+      <c r="H84" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="J84" s="8" t="s">
+      <c r="I84" s="11" t="s">
         <v>382</v>
       </c>
+      <c r="J84" s="11" t="s">
+        <v>383</v>
+      </c>
       <c r="K84" s="13"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8" t="s">
-        <v>23</v>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -8000,35 +8021,35 @@
       <c r="A85" s="2">
         <v>3</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C85" s="8" t="s">
+      <c r="B85" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C85" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H85" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="12"/>
+      <c r="F85" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="I85" s="8" t="s">
+      <c r="G85" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H85" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="J85" s="8" t="s">
+      <c r="I85" s="11" t="s">
         <v>386</v>
       </c>
+      <c r="J85" s="11" t="s">
+        <v>387</v>
+      </c>
       <c r="K85" s="13"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8" t="s">
-        <v>29</v>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -8037,34 +8058,34 @@
       <c r="A86" s="2">
         <v>3</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C86" s="8" t="s">
+      <c r="B86" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C86" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="G86" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="12"/>
+      <c r="F86" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="H86" s="8" t="s">
+      <c r="G86" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="I86" s="8" t="s">
+      <c r="H86" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="J86" s="8" t="s">
+      <c r="I86" s="11" t="s">
         <v>391</v>
       </c>
+      <c r="J86" s="11" t="s">
+        <v>392</v>
+      </c>
       <c r="K86" s="13"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="8" t="s">
+      <c r="L86" s="11"/>
+      <c r="M86" s="11" t="s">
         <v>41</v>
       </c>
       <c r="N86" s="2"/>
@@ -8074,35 +8095,35 @@
       <c r="A87" s="2">
         <v>3</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C87" s="8" t="s">
+      <c r="B87" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C87" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H87" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="12"/>
+      <c r="F87" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="G87" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I87" s="8" t="s">
+      <c r="H87" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="J87" s="8" t="s">
+      <c r="I87" s="11" t="s">
         <v>88</v>
       </c>
+      <c r="J87" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="K87" s="13"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8" t="s">
-        <v>23</v>
+      <c r="L87" s="11"/>
+      <c r="M87" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -8111,37 +8132,37 @@
       <c r="A88" s="2">
         <v>4.3</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>393</v>
+      <c r="B88" s="12" t="s">
+        <v>394</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E88" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E88" s="12"/>
       <c r="F88" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I88" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J88" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K88" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L88" s="15"/>
       <c r="M88" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -8150,35 +8171,35 @@
       <c r="A89" s="2">
         <v>4.2</v>
       </c>
-      <c r="B89" s="9" t="s">
-        <v>401</v>
+      <c r="B89" s="12" t="s">
+        <v>402</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E89" s="12"/>
       <c r="F89" s="16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K89" s="15"/>
       <c r="L89" s="15"/>
       <c r="M89" s="15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -8187,35 +8208,35 @@
       <c r="A90" s="2">
         <v>4.2</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>401</v>
+      <c r="B90" s="12" t="s">
+        <v>402</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E90" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E90" s="12"/>
       <c r="F90" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K90" s="15"/>
       <c r="L90" s="15"/>
       <c r="M90" s="15" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -8224,30 +8245,30 @@
       <c r="A91" s="2">
         <v>4.2</v>
       </c>
-      <c r="B91" s="9" t="s">
-        <v>401</v>
+      <c r="B91" s="12" t="s">
+        <v>402</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E91" s="12"/>
       <c r="F91" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I91" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K91" s="15"/>
       <c r="L91" s="15"/>
@@ -8261,35 +8282,35 @@
       <c r="A92" s="2">
         <v>4.1</v>
       </c>
-      <c r="B92" s="9" t="s">
-        <v>418</v>
+      <c r="B92" s="12" t="s">
+        <v>419</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E92" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E92" s="12"/>
       <c r="F92" s="16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I92" s="15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K92" s="15"/>
       <c r="L92" s="15"/>
       <c r="M92" s="15" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -8298,35 +8319,35 @@
       <c r="A93" s="2">
         <v>4.1</v>
       </c>
-      <c r="B93" s="9" t="s">
-        <v>418</v>
+      <c r="B93" s="12" t="s">
+        <v>419</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E93" s="12"/>
       <c r="F93" s="16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H93" s="16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I93" s="16" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J93" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K93" s="15"/>
       <c r="L93" s="15"/>
       <c r="M93" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -8335,35 +8356,35 @@
       <c r="A94" s="2">
         <v>4.1</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>418</v>
+      <c r="B94" s="12" t="s">
+        <v>419</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E94" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E94" s="12"/>
       <c r="F94" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H94" s="16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I94" s="16" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J94" s="16" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K94" s="15"/>
       <c r="L94" s="15"/>
       <c r="M94" s="15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -8372,37 +8393,37 @@
       <c r="A95" s="2">
         <v>4.3</v>
       </c>
-      <c r="B95" s="9" t="s">
-        <v>393</v>
+      <c r="B95" s="12" t="s">
+        <v>394</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E95" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E95" s="12"/>
       <c r="F95" s="16" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H95" s="16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I95" s="16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J95" s="16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K95" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="L95" s="9"/>
-      <c r="M95" s="7" t="s">
         <v>442</v>
+      </c>
+      <c r="L95" s="12"/>
+      <c r="M95" s="10" t="s">
+        <v>443</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -8411,26 +8432,26 @@
       <c r="A96" s="2">
         <v>5</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C96" s="7" t="s">
+      <c r="B96" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C96" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E96" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E96" s="12"/>
       <c r="F96" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="9"/>
-      <c r="J96" s="9"/>
-      <c r="K96" s="9"/>
-      <c r="L96" s="9"/>
-      <c r="M96" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N96" s="2"/>
@@ -8440,26 +8461,26 @@
       <c r="A97" s="2">
         <v>5</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C97" s="7" t="s">
+      <c r="B97" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C97" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D97" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E97" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E97" s="12"/>
       <c r="F97" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9"/>
-      <c r="L97" s="9"/>
-      <c r="M97" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
+      <c r="M97" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N97" s="2"/>
@@ -8469,26 +8490,26 @@
       <c r="A98" s="2">
         <v>5</v>
       </c>
-      <c r="B98" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C98" s="7" t="s">
+      <c r="B98" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C98" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E98" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E98" s="12"/>
       <c r="F98" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
-      <c r="M98" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12"/>
+      <c r="M98" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N98" s="2"/>
@@ -8498,26 +8519,26 @@
       <c r="A99" s="2">
         <v>5</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C99" s="7" t="s">
+      <c r="B99" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C99" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D99" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E99" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E99" s="12"/>
       <c r="F99" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
-      <c r="K99" s="9"/>
-      <c r="L99" s="9"/>
-      <c r="M99" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+      <c r="M99" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N99" s="2"/>
@@ -8527,26 +8548,26 @@
       <c r="A100" s="2">
         <v>5</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C100" s="7" t="s">
+      <c r="B100" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C100" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E100" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E100" s="12"/>
       <c r="F100" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
-      <c r="M100" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="12"/>
+      <c r="L100" s="12"/>
+      <c r="M100" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N100" s="2"/>
@@ -8556,26 +8577,26 @@
       <c r="A101" s="2">
         <v>5</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C101" s="7" t="s">
+      <c r="B101" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C101" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D101" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E101" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E101" s="12"/>
       <c r="F101" s="16" t="s">
-        <v>450</v>
-      </c>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="9"/>
-      <c r="J101" s="9"/>
-      <c r="K101" s="9"/>
-      <c r="L101" s="9"/>
-      <c r="M101" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="12"/>
+      <c r="L101" s="12"/>
+      <c r="M101" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N101" s="2"/>
@@ -8585,26 +8606,26 @@
       <c r="A102" s="2">
         <v>5</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C102" s="7" t="s">
+      <c r="B102" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C102" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D102" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E102" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E102" s="12"/>
       <c r="F102" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="9"/>
-      <c r="J102" s="9"/>
-      <c r="K102" s="9"/>
-      <c r="L102" s="9"/>
-      <c r="M102" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
+      <c r="I102" s="12"/>
+      <c r="J102" s="12"/>
+      <c r="K102" s="12"/>
+      <c r="L102" s="12"/>
+      <c r="M102" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N102" s="2"/>
@@ -8614,26 +8635,26 @@
       <c r="A103" s="2">
         <v>5</v>
       </c>
-      <c r="B103" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C103" s="7" t="s">
+      <c r="B103" s="10" t="s">
         <v>444</v>
       </c>
+      <c r="C103" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="D103" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E103" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="E103" s="12"/>
       <c r="F103" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="9"/>
-      <c r="M103" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="G103" s="12"/>
+      <c r="H103" s="12"/>
+      <c r="I103" s="12"/>
+      <c r="J103" s="12"/>
+      <c r="K103" s="12"/>
+      <c r="L103" s="12"/>
+      <c r="M103" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N103" s="2"/>
@@ -8645,14 +8666,14 @@
       <c r="C104" s="17"/>
       <c r="D104" s="3"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="5"/>
-      <c r="M104" s="5"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+      <c r="M104" s="7"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
     </row>
@@ -8662,14 +8683,14 @@
       <c r="C105" s="17"/>
       <c r="D105" s="3"/>
       <c r="E105" s="2"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5"/>
-      <c r="M105" s="5"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+      <c r="M105" s="7"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
     </row>
@@ -8679,14 +8700,14 @@
       <c r="C106" s="17"/>
       <c r="D106" s="3"/>
       <c r="E106" s="2"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7"/>
+      <c r="M106" s="7"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
     </row>
